--- a/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_master_buy_list_line_by_line_v3_20260415.xlsx
+++ b/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_master_buy_list_line_by_line_v3_20260415.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2444,17 +2444,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fuse box - Compact covered ATO/ATC fuse block 6-way</t>
+          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>3 identical</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor fuse boxes or new compact covered aftermarket</t>
+          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PKR 11100-21000</t>
+          <t>PKR 54000-136000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2479,39 +2479,39 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Covered body, firm lid, strong terminals</t>
+          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>229</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Reuse original Toyota-style boxes only if terminals are tight and no heat damage.</t>
+          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
+          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>Full set</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
+          <t>New parts market only (no used donor plugs)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2521,54 +2521,54 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>PKR 54000-136000</t>
+          <t>PKR 12000-36000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260317_235150.jpg</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BUY_IF_ENGINE_CODE_MATCH</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
+          <t>New only; no used/refurbished plugs</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260317_235150.jpg</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
+          <t>No. Glow/heat plugs should be new only.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
+          <t>Front leaf spring pack - Measure eye-eye, width, arch, center pin, bush ID, eye width</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Full set</t>
+          <t>2 packs</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>New parts market only (no used donor plugs)</t>
+          <t>Local spring fabricator / suspension shop (new fabricated to measurement)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2578,44 +2578,44 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-36000</t>
+          <t>PKR 35000-90000</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>images/20260317_235150.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>BUY_IF_ENGINE_CODE_MATCH</t>
+          <t>MEASURE_THEN_BUY</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>New only; no used/refurbished plugs</t>
+          <t>Buy only after measured fit confirmation</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20260317_235150.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>No. Glow/heat plugs should be new only.</t>
+          <t>Maybe. Existing springs can stay if arch, eye bushes, and crack check pass; otherwise replace/fabricate.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Front leaf spring pack - Measure eye-eye, width, arch, center pin, bush ID, eye width</t>
+          <t>Rear leaf spring pack - Measure eye-eye, width, arch, center pin, bush ID, eye width</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>20260324_004852.jpg;20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2672,17 +2672,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Rear leaf spring pack - Measure eye-eye, width, arch, center pin, bush ID, eye width</t>
+          <t>OME/EMU front shock pair - OME-60097 x2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2 packs</t>
+          <t>2 shocks (1 front pair)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Local spring fabricator / suspension shop (new fabricated to measurement)</t>
+          <t>OME/EMU importer or off-road parts supplier (new genuine preferred)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>PKR 35000-90000</t>
+          <t>PKR 55000-110000</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2702,39 +2702,39 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_THEN_BUY</t>
+          <t>QUOTE_ONLY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Buy only after measured fit confirmation</t>
+          <t>Part number stamping OME-60097, eye/bush size, compressed/extended length, genuine packaging</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220214.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33-A</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Existing springs can stay if arch, eye bushes, and crack check pass; otherwise replace/fabricate.</t>
+          <t>N/A optional upgrade. Existing suspension can be retained if serviceable and ride goals are acceptable.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>OME/EMU front shock pair - OME-60097 x2</t>
+          <t>OME/EMU rear shock pair - OME-63064 x2</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2 shocks (1 front pair)</t>
+          <t>2 shocks (1 rear pair)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Part number stamping OME-60097, eye/bush size, compressed/extended length, genuine packaging</t>
+          <t>Part number stamping OME-63064, eye/bush size, compressed/extended length, genuine packaging</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>33-A</t>
+          <t>33-B</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>OME/EMU rear shock pair - OME-63064 x2</t>
+          <t>OME shackle front - OMEGS8 (front, legacy note: pre-1980/15mm pin)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2 shocks (1 rear pair)</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PKR 55000-110000</t>
+          <t>PKR 25000-60000</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>images/20260411_220207.jpg</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Part number stamping OME-63064, eye/bush size, compressed/extended length, genuine packaging</t>
+          <t>Confirm pin dia and compatibility</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>33-B</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>OME shackle front - OMEGS8 (front, legacy note: pre-1980/15mm pin)</t>
+          <t>OME shackle rear - OMEGS9 (rear)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PKR 25000-60000</t>
+          <t>PKR 25000-65000</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_220207.jpg</t>
+          <t>images/20260411_220214.jpg</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20260411_220207.jpg</t>
+          <t>20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>OME shackle rear - OMEGS9 (rear)</t>
+          <t>OME bush kit - OMESB30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>4 kits</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PKR 25000-65000</t>
+          <t>PKR 28000-60000</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_220214.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2935,17 +2935,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Confirm pin dia and compatibility</t>
+          <t>Confirm bush count per spring-eye set</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20260411_220214.jpg</t>
+          <t>20260324_004852.jpg</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>OME bush kit - OMESB30</t>
+          <t>OME U-bolt kit - OMEU59A</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>4 kits</t>
+          <t>7 kits</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PKR 28000-60000</t>
+          <t>PKR 42000-98000</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>images/20260411_220207.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Confirm bush count per spring-eye set</t>
+          <t>Confirm rod dia, width, leg length, pitch</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg</t>
+          <t>20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3014,17 +3014,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>OME U-bolt kit - OMEU59A</t>
+          <t>Steering bushings - Steering linkage bush set</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>7 kits</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>OME/EMU importer or off-road parts supplier (new genuine preferred)</t>
+          <t>New hardware/electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>PKR 42000-98000</t>
+          <t>PKR 3000-12000</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_220207.jpg</t>
+          <t>images/20260406_031010.jpg</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3049,39 +3049,39 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Confirm rod dia, width, leg length, pitch</t>
+          <t>Condition-based quote</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20260411_220207.jpg</t>
+          <t>20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>230</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>N/A optional upgrade. Existing suspension can be retained if serviceable and ride goals are acceptable.</t>
+          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Steering bushings - Steering linkage bush set</t>
+          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1 set</t>
+          <t>3 segments</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>New hardware/electrical market (not donor car)</t>
+          <t>Electrical workshop service (rework existing wires)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3091,64 +3091,64 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000</t>
+          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>images/20260406_031010.jpg</t>
+          <t>images/20260411_065030.jpg</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_ONLY</t>
+          <t>WORKSHOP_TASK</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Condition-based quote</t>
+          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20260406_031010.jpg</t>
+          <t>20260411_065030.jpg;20260321_235600.jpg</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>Electrical_Master</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
+          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
+          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>3 segments</t>
+          <t>10 rolls</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Electrical workshop service (rework existing wires)</t>
+          <t>New electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
+          <t>PKR 1500-4500</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3158,39 +3158,39 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP_TASK</t>
+          <t>BUY_NOW</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
+          <t>Good adhesive and heat tolerance, not brittle PVC</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260321_235600.jpg</t>
+          <t>20260411_065030.jpg</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Electrical_Master</t>
+          <t>SUB-17</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
+          <t>N/A consumable item; buy new.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
+          <t>Cloth harness loom tape (Tesa-style)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>10 rolls</t>
+          <t>5 rolls</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PKR 1500-4500</t>
+          <t>PKR 2500-9000</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Good adhesive and heat tolerance, not brittle PVC</t>
+          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>SUB-17</t>
+          <t>SUB-23</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Cloth harness loom tape (Tesa-style)</t>
+          <t>Firewall grommet assortment</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>5 rolls</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3257,17 +3257,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PKR 2500-9000</t>
+          <t>PKR 2000-7000</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260411_143135.jpg</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
+          <t>Hole ID/OD fit and thickness for firewall panels</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg</t>
+          <t>20260411_143135.jpg</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>SUB-23</t>
+          <t>SUB-11</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3299,17 +3299,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Firewall grommet assortment</t>
+          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>New electrical market (not donor car)</t>
+          <t>Toyota donor car (Bilal Ganj)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3319,44 +3319,44 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PKR 2000-7000</t>
+          <t>PKR 60000-150000</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_143135.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>QUOTE_ONLY</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Hole ID/OD fit and thickness for firewall panels</t>
+          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>SUB-11</t>
+          <t>229-C1</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N/A consumable item; buy new.</t>
+          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PKR 60000-150000</t>
+          <t>PKR 55000-140000</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
+          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>229-C1</t>
+          <t>229-C2</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>PKR 55000-140000</t>
+          <t>PKR 50000-130000</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
+          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3458,67 +3458,10 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>229-C2</t>
+          <t>229-C3</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>1 complete kit</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Toyota donor car (Bilal Ganj)</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>PKR 50000-130000</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>images/20260321_235600.jpg</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>QUOTE_ONLY</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>229-C3</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
         </is>
